--- a/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-startup-checklist.xlsx
+++ b/astro-site/public/dl/wedding-venue-business-plan/wedding-venue-startup-checklist.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>The build-out goes on land you don't own, so the term, counting renewal options, should be at least as long as your loan: SBA lenders typically require this; confirm with your lender. Aim for a term long enough to recover your investment.</t>
+          <t>The build-out goes on land you don't own, so the term, counting renewal options that only you can exercise, should be at least as long as your loan: SBA lenders typically require this; confirm with your lender. Aim for a term long enough to recover your investment.</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>A guided tour, the brochure and a referral commission agreed in writing. The plan assumes one in five sales comes through them. Venue marketplaces such as Peerspace can add corporate and private events.</t>
+          <t>A guided tour, the brochure and a referral commission agreed in writing. The plan assumes one in ten sales comes through planners and venue marketplaces, at a 15% commission. Marketplaces such as Peerspace can add corporate and private events.</t>
         </is>
       </c>
     </row>
